--- a/event_registration_forms/017_healthy_sexuality_event_registration--event_registration_forms.xlsx
+++ b/event_registration_forms/017_healthy_sexuality_event_registration--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1154,8 +1154,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Workshop'}</t>
+          <t>Workshop</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'session'}</t>
+          <t>session</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Session'}</t>
+          <t>Session</t>
         </is>
       </c>
     </row>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1251,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1268,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non_vegetarian'}</t>
+          <t>non_vegetarian</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non Vegetarian'}</t>
+          <t>Non Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1319,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
